--- a/assets/kinyu-juku.xlsx
+++ b/assets/kinyu-juku.xlsx
@@ -798,7 +798,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ご記入いただく欄は全部で 30 です（うち【必須】は 9 ）。</t>
+          <t>ご記入いただく欄は全部で 31 です（うち【必須】は 9 ）。</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E52"/>
+  <dimension ref="A2:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1630,6 +1630,24 @@
         </is>
       </c>
     </row>
+    <row r="53" ht="78" customHeight="1">
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>杜工舎の制作例として紹介してよいか</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr"/>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>選ぶだけ（任意）</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>「紹介してよい」とお書きいただいた場合だけ、杜工舎のホームページの制作例として、御社の社名とページへのリンクを載せます。空欄なら載せません。お礼や値引きはなく、お断りいただいても制作の内容は変わりません。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/kinyu-juku.xlsx
+++ b/assets/kinyu-juku.xlsx
@@ -798,7 +798,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ご記入いただく欄は全部で 31 です（うち【必須】は 9 ）。</t>
+          <t>ご記入いただく欄は全部で 30 です（うち【必須】は 9 ）。</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E53"/>
+  <dimension ref="A2:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1630,24 +1630,6 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="78" customHeight="1">
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>杜工舎の制作例として紹介してよいか</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr"/>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>選ぶだけ（任意）</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>「紹介してよい」とお書きいただいた場合だけ、杜工舎のホームページの制作例として、御社の社名とページへのリンクを載せます。空欄なら載せません。お礼や値引きはなく、お断りいただいても制作の内容は変わりません。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
